--- a/Result/profitability/5202.xlsx
+++ b/Result/profitability/5202.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.04</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.17625</v>
+        <v>-0.2625</v>
       </c>
       <c r="N2" t="n">
-        <v>78.08875</v>
+        <v>78.17375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.26</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.12125</v>
+        <v>-0.1825</v>
       </c>
       <c r="N3" t="n">
-        <v>80.61</v>
+        <v>80.2675</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.2</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.04875</v>
+        <v>-0.11375</v>
       </c>
       <c r="N4" t="n">
-        <v>81.19749999999999</v>
+        <v>80.78125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.31</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.04375000000000001</v>
+        <v>-0.11</v>
       </c>
       <c r="N5" t="n">
-        <v>85.22500000000001</v>
+        <v>83.71250000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.17</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01999999999999999</v>
+        <v>-0.1025</v>
       </c>
       <c r="N6" t="n">
-        <v>86.17125</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,13 +1264,13 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.006249999999999993</v>
+        <v>-0.0975</v>
       </c>
       <c r="N7" t="n">
-        <v>88.48375</v>
+        <v>87.82250000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.18</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03374999999999999</v>
+        <v>-0.05125</v>
       </c>
       <c r="N8" t="n">
-        <v>90.69625000000001</v>
+        <v>90.68625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1650,7 +1650,7 @@
         <v>0.07499999999999998</v>
       </c>
       <c r="N10" t="n">
-        <v>94.21000000000001</v>
+        <v>94.20999999999999</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -2033,7 +2033,7 @@
         <v>0.09874999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>95.785</v>
+        <v>95.78500000000001</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5202</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>39</v>
+      </c>
+      <c r="D75" t="n">
+        <v>11</v>
+      </c>
+      <c r="E75" t="n">
+        <v>28</v>
+      </c>
+      <c r="F75" t="n">
+        <v>72.23999999999999</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-18</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-44.83%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-59</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-77</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-77</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="N75" t="n">
+        <v>75.36875000000001</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.6799999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>3.578947368421052</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.07999999999999829</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.001106194690265516</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.558823529411764</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-12.10000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.143466919611098</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
